--- a/internal_doc/05.测试设计/参数校验/测试用例/元数据（CL）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/元数据（CL）参数校验测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="102">
   <si>
     <t>name</t>
   </si>
@@ -82,108 +82,271 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">1、首次创建name唯一的CS，创建成功
-2、重复创建相同name的CS，创建失败，返回结果报错，并提示CS名已存在，提示信息合理准确
-</t>
-  </si>
-  <si>
-    <t>1、CS创建失败，提示参数不合法，提示信息合理准确
-2、日志打印信息合理准确</t>
-  </si>
-  <si>
-    <t>1、CS创建失败，提示参数超出长度，提示信息合理准确
-2、日志打印信息合理准确</t>
-  </si>
-  <si>
-    <t>1、CS创建失败，提示参数错误，提示信息合理准确
-2、日志打印信息合理准确</t>
-  </si>
-  <si>
-    <t>1、CS创建失败，提示系统CS不能删除，提示信息合理准确
-2、日志打印信息合理准确</t>
-  </si>
-  <si>
-    <t>1、CS获取失败，提示参数错误，提示信息合理准确
-2、日志打印信息合理准确</t>
-  </si>
-  <si>
-    <t>1、CS获取成功，指定的CS被直接忽略，返回结果显示所有CS（非系统CS）</t>
-  </si>
-  <si>
-    <t>1、sdb运行正常
-2、sdb已存在数据组group1、group2、group3
-3、sdb已存在域domain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CS，输入name、PageSize、Domain、LobPageSize有效参数创建CS，规格如下：
+    <t>createCL，name重复</t>
+  </si>
+  <si>
+    <t>createCL，name字符无效</t>
+  </si>
+  <si>
+    <t>createCL，name长度无效</t>
+  </si>
+  <si>
+    <t>createCL，name参数不存在</t>
+  </si>
+  <si>
+    <t>createCL，格式错误</t>
+  </si>
+  <si>
+    <t>语法：db.collectionspace.createCL(&lt; name &gt;,[ options ])
+参数规格：
+name：string，必填，全局唯一，不能是空串，含点（.）或者美元符号（$）。且长度不超过127B。
+options，非必填</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，覆盖options:ReplSize有效字符和边界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，覆盖options:Compressed有效字符和边界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，覆盖options:IsMainCL有效字符和边界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，覆盖options:Group有效字符和边界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，覆盖options:AutoIndexId有效字符和边界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReplSize: &lt; int num &gt;
+默认副本写入个数为1；取值为0，则副本数等于数据组节点个数；手动指定副本写入个数时，不能超出当前组内节点个数。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Group必须存在于集合空间所属的域中（所有复制组均属于SYSDOMAIN，即如果集合空间没有指定域，则系统内任意复制组均可）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，覆盖name有效字符和边界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入name、PageSize、Domain、LobPageSize有效参数创建CL，规格如下：
 name覆盖如下取值：
   a.1字节的有效字符，如：a 或 *
   b.127字节的有效字符，覆盖所有支持的有效字符，如：“123-test-中文。~!@#%^&amp;*()_+-=\][{}|,/&lt;&gt;?~·！@#￥%……&amp;*（）——+《》{}|【】、，。、~_127B”
-PageSize覆盖如下取值：0、4096、8192、16384、32768、65536
-Domain覆盖如下取值:已存在的CS，非系统CS
-LobPageSize覆盖如下取值：0、4096、8192、16384、32768、65536、131072、262144、524288
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CS创建成功，执行db.listCollectionSpaces或db.snapshot可以查看到新创建的CS。
-检查PageSize、LobPageSize默认取值。
-2、在CS下创建CL，CL创建成功。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CS创建失败，提示域不存在，提示信息合理准确
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入有效的name、groups、Autosplit创建CL，如：
+db.createCL("testCL")
+2、重复步骤1，创建name相同的CL
+3、检查执行结果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1、首次创建name唯一的CL，创建成功
+2、重复创建相同name的CL，创建失败，返回结果报错，并提示CL名已存在，提示信息合理准确
+</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入name字符无效，覆盖如下无效取值：
+  a.包含（.）
+  b.包含$
+如：
+db.createCL('test.CL')
+db.createCL('test$CL')
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、CL创建失败，提示参数不合法，提示信息合理准确
 2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropCS，删除系统CS</t>
-  </si>
-  <si>
-    <t>dropCS，指定CS名为空</t>
-  </si>
-  <si>
-    <t>1、进入sdb，删除CS，CS名为空，覆盖如下取值：
-db.dropCS("")
-db.dropCS()
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>语法：db.dropCS(&lt; name &gt;)
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入name长度无效，覆盖如下无效取值：
+  a.空串
+  b.128字节
+如：
+db.createCL('')  或  db.createCL()   或  为128字节的有效字符
+3、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、CL创建失败，提示参数超出长度，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，不输入name，如：
+db.createCL({PageSize:4096,Domain:"domain"})
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、CL创建失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>dropCL，删除为空和不为空的CL</t>
+  </si>
+  <si>
+    <t>1、进入sdb，删除为空和不为空的CL，如：
+db.dropCL("testCL_01"),其中testCL_01中存在CL
+db.dropCL("testCL_02"),其中testCL_02中不存在CL
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、CL删除成功，db.list(4)或db.list(5)查看CL以及CL下CL已全部删除
+2、查看CL相关配置文件已删除干净</t>
+  </si>
+  <si>
+    <t>dropCL，删除不存在的CL</t>
+  </si>
+  <si>
+    <t>语法：db.dropCL(&lt; name &gt;)
 参数规格：
-name：string，必填，CS必须存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，删除不存在的CS，如：
-db.dropCS("testCS"),其中testCS在sdb不存在
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>dropCS，删除不存在的CS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropCS，删除为空和不为空的CS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，删除为空和不为空的CS，如：
-db.dropCS("testCS_01"),其中testCS_01中存在CL
-db.dropCS("testCS_02"),其中testCS_02中不存在CL
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CS创建失败，提示CS不存在，提示信息合理准确
+name：string，必填，CL必须存在</t>
+  </si>
+  <si>
+    <t>1、进入sdb，删除不存在的CL，如：
+db.dropCL("testCL"),其中testCL在sdb不存在
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、CL创建失败，提示CL不存在，提示信息合理准确
 2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>dropCL，删除系统CL</t>
+  </si>
+  <si>
+    <t>1、进入sdb，删除系统CL，如：
+db.dropCL("testCL"),其中testCL为系统CL
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、CL创建失败，提示系统CL不能删除，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>dropCL，指定CL名为空</t>
+  </si>
+  <si>
+    <t>1、进入sdb，删除CL，CL名为空，覆盖如下取值：
+db.dropCL("")
+db.dropCL()
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>getCL，获取不存在的CL</t>
+  </si>
+  <si>
+    <t>语法：db.getCL(&lt; name &gt;)
+参数规格：
+name：string，必填，获取已存在的CL。不能获取系统CL。</t>
+  </si>
+  <si>
+    <t>1、进入sdb，获取指定CL，不指定CL名，如：
+db.dropCL("testCL")，其中testCL在sdb不存在
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、CL获取失败，提示CL不存在，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>getCL，指定的CL名为空</t>
+  </si>
+  <si>
+    <t>1、进入sdb，获取指定的CL，CL名为空，覆盖如下取值：
+db.getCL("")
+db.getCL()
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、CL获取失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>1、CL获取成功，指定的CL被直接忽略，返回结果显示所有CL（非系统CL）</t>
+  </si>
+  <si>
+    <t>listCollections，加条件查询</t>
+  </si>
+  <si>
+    <t>语法：db.listCollections()
+无参数</t>
+  </si>
+  <si>
+    <t>1、进入sdb，获取所有CL（非系统CL），指定CL名，覆盖如下取值：
+  a.指定已存在的CL名
+  b.空串
+如：
+db.listCollections("testCL")，其中testCL在sdb存在
+db.listCollections("")
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、CL创建成功，执行db.listCollections或db.snapshot可以查看到新创建的CL。
+检查ShardingKey、ShardingType、Partition、ReplSize、Compressed、IsMainCL、AutoSplit、Group、AutoIndexId默认取值正确。
+2、在CL下插入数据，数据插入成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在数据组group1、group2、group3
+3、sdb已存在域domain
+4、sdb已存在testCS，且指定域为domian</t>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在数据组group1、group2、group3
+3、sdb已存在域domain，该域有指定多个组
+4、sdb已存在testCS，且指定域为domian</t>
+  </si>
+  <si>
+    <t>createCL，覆盖options:ShardingKey/ShardingType/Partition/AutoSplit有效字符和边界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:ShardingKey
+格式：ShardingKey:{&lt; 字段1 &gt; : &lt; 1|-1 &gt;,[&lt; 字段2 &gt;:&lt; 1|-1 &gt;, ...]}
+需要分区，必须指定ShardingKey
+options:ShardingType,默认为hash分区
+ShardingType:"hash"|"range"
+options:AutoSplit,bool:true|false
+AutoSplit必须配合散列分区和域使用，且不能与Group同时使用。如果在集合中没有指定AutoSplit，则使用所属域中的AutoSplit参数
+options:Partition，hash 分区时填写，代表了 hash 分区的个数。其值必须是2的幂。范围在[2^3, 2^20]，即为8~1048576范围内2的幂次方取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入name、options:ShardingKey/ShardingType/AutoSplit有效参数创建CL，规格如下：
+name取任意有效值；
+options:ShardingKey覆盖如下取值：
+  a.单分区键，取值1|-1
+  b.多分区键，取值1|-1
+options:ShardingType覆盖如下取值：
+  a.ShardingType:"hash"
+  b.ShardingType:"range"
+options:Partition覆盖如下取值：
+  a.hash分区，有效取值：8、1048576
+options:AutoSplit覆盖如下取值：
+  a.hash分区，AutoSplit:true，且不指定Group
+  b.hash分区，AutoSplit:false
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CL创建成功，执行db.listCollections或db.snapshot可以查看到新创建的CL。
+2、在CL插入批量数据，检查数据分区正确，如指定hash分区范围并指定自动切分创建CL，插入数据后数据自动按切分条件正确切分，各数据组数据正确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>1、CS删除成功，db.list(4)或db.list(5)查看CS以及CS下CL已全部删除
-2、查看</t>
+      <t>1、CL创建成功，执行db.listCollections或db.snapshot可以查看到新创建的CL。
+2、在CL插入批量数据，</t>
     </r>
     <r>
       <rPr>
@@ -194,188 +357,190 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>CS相关配置文件</t>
+      <t>检查写数据按创建CL是设置的ReplSize返回结果</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>已删除干净</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，删除系统CS，如：
-db.dropCS("testCS"),其中testCS为系统CS
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getCS，获取不存在的CS</t>
-  </si>
-  <si>
-    <t>语法：db.getCS(&lt; name &gt;)
-参数规格：
-name：string，必填，获取已存在的CS。不能获取系统CS。</t>
-  </si>
-  <si>
-    <t>getCS，指定的CS名为空</t>
-  </si>
-  <si>
-    <t>1、进入sdb，获取指定的CS，CS名为空，覆盖如下取值：
-db.getCS("")
-db.getCS()
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、CS获取失败，提示CS不存在，提示信息合理准确
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入name、options:ReplSize有效参数创建CL，规格如下：
+  name取任意有效值；
+  options:ReplSize覆盖如下取值：0、-1（当前活动的节点）、7、取值等于数据组节点个数
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入name、options:Compressed有效参数创建CL，规格如下：
+  name取任意有效值；
+  options:Compressed覆盖如下取值：true|false
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否为主表，IsMainCL:true|false</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否做数据压缩，Compressed:true|false</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CL创建成功，执行db.listCollections或db.snapshot可以查看到新创建的CL。
+2、配置Compressed为true则插入数据时压缩存入；配置Compressed为false则插入数据时不压缩存入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入name、options:IsMainCL有效参数创建CL，规格如下：
+  name取任意有效值；
+  options:IsMainCL覆盖如下取值：true|false
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CL创建成功，执行db.listCollections或db.snapshot可以查看到新创建的CL。
+2、配置IsMainCL为true则创建的表为主表；配置IsMainCL为false则创建的表为普通表。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入name、options:GroupL有效参数创建CL，规格如下：
+name取任意有效值；
+options:Group覆盖如下取值：
+  a.所属CS指定域，指定CL的Group为CS所属域中的group
+  b.所属CS不指定域，指定CL的Group为系统内任意复制组
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CL创建成功，执行db.listCollections或db.snapshot可以查看到新创建的CL。检查CL关联的组为创建CL时指定的组。
+2、插入数据，数据全部落到指定组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入name、options:AutoIndexId有效参数创建CL，规格如下：
+  name取任意有效值；
+  options:AutoIndexId覆盖如下取值：true|false
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否自动创建 _id 索引，AutoIndexId:true|false</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CL创建成功，执行db.listCollections或db.snapshot可以查看到新创建的CL。
+2、配置AutoIndexId为true则自动创建 _id 索引，执行db.collectionspace.collection.listIndexes()查看有_id索引，索引创建正确；
+配置AutoIndexId为false则不自动创建 _id 索引，执行db.collectionspace.collection.listIndexes()查看没有_id索引。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:ShardingKey无效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:ShardingKey为空串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入ShardingKey无效取值，如：
+db.testCS.createCL("testCL",{ShardingKey:{"age":0}}  
+db.testCS.createCL("testCL",{ShardingKey:{"age":"-1"}} 
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:ShardingType为空串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:ShardingType取值非bool型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入ShardingKey为空串，如：
+db.testCS.createCL("testCL",{ShardingKey:{"age":""}}) 
+db.testCS.createCL("testCL",{ShardingKey:{"age":}})
+db.testCS.createCL("testCL",{ShardingKey:{}})  
+db.testCS.createCL("testCL",{ShardingKey:}) 
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入ShardingType取值非bool型，如：
+db.testCS.createCL("testCL",{ShardingKey:{"age":"test"}})   
+db.testCS.createCL("testCL",{ShardingKey:{"age":"Y"}})  
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:Partition无效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入ShardingKey为空串，如：
+db.testCS.createCL("testCL",{ShardingKey:{"age":1,ShardingType:""}) 
+db.testCS.createCL("testCL",{ShardingKey:{"age":1,ShardingType:}}) 
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:Partition取值为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CL创建失败，提示参数错误，提示信息合理准确
 2、日志打印信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，获取指定CS，不指定CS名，如：
-db.dropCS("testCS")，其中testCS在sdb不存在
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>listCollectionSpaces，加条件查询</t>
-  </si>
-  <si>
-    <t>语法：db.listCollectionSpaces()
-无参数</t>
-  </si>
-  <si>
-    <t>1、进入sdb，获取所有CS（非系统CS），指定CS名，覆盖如下取值：
-  a.指定已存在的CS名
-  b.空串
+    <t>1、进入sdb，创建CL，Partition无效取值，覆盖如下取值：
+  a.取值为：4(2^2)、2097152（2^21）、7、1048577
+  b.range分区，Partition取有效值，如1024
 如：
-db.listCollectionSpaces("testCS")，其中testCS在sdb存在
-db.listCollectionSpaces("")
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，name重复</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CS，输入有效的name、groups、Autosplit创建CS，如：
-db.createCL("testCS")
-2、重复步骤1，创建name相同的CS
-3、检查执行结果</t>
-  </si>
-  <si>
-    <t>createCL，name字符无效</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CS，输入name字符无效，覆盖如下无效取值：
-  a.包含（.）
-  b.包含$
-如：
-db.createCL('test.cs')
-db.createCL('test$cs')
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>createCL，name长度无效</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CS，输入name长度无效，覆盖如下无效取值：
-  a.空串
-  b.128字节
-如：
-db.createCL('')  或  db.createCL()   或  为128字节的有效字符
-3、检查执行结果</t>
-  </si>
-  <si>
-    <t>createCL，name参数不存在</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CS，不输入name，如：
-db.createCL({PageSize:4096,Domain:"domain"})
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>createCL，options:PageSize无效取值</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CS，输入PageSize无效取值，覆盖如下取值：
-  a.无效取值：4096.5、-4096、4096.
-  b.空串
-如：
-db.createCL('testCS',{PageSize:4096.5})  
-db.createCL('testCS',{PageSize:})
-3、检查执行结果</t>
-  </si>
-  <si>
-    <t>createCL，options:Domain指定的域不存在</t>
-  </si>
-  <si>
-    <t>1、进入sdb，options:Domain指定的域不存在，如：
-db.createCL('testCS',{Domain:dm})，其中dm在sdb不存在
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>createCL，options:Domain指定的域为系统域</t>
-  </si>
-  <si>
-    <t>1、进入sdb，options:Domain指定的域为系统域，如：
-db.createCL('testCS',{Domain:dm})，其中dm为系统域
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>createCL，options:Domain取值为空串</t>
-  </si>
-  <si>
-    <t>1、进入sdb，options:Domain取值为空串，如：
-db.createCL('testCS',{Domain:})
-db.createCL('testCS',{Domain:''})
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>createCL，options:LobPageSize无效取值</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CS，输入LobPageSize无效取值，覆盖如下取值：
-  a.无效取值：4096.5、-4096、4096.
-  b.空串
-如：
-db.createCL('testCS',{LobPageSize:4096.5})  
-db.createCL('testCS',{LobPageSize:})
-db.createCL('testCS',{LobPageSize:''})
-3、检查执行结果</t>
-  </si>
-  <si>
-    <t>createCL，格式错误</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CS，参数格式错误，覆盖如下参数格式：
+db.testCS.createCL("testCL",{ShardingKey:{"age":1,ShardingType:"hash",Partition:4}) 
+db.testCS.createCL("testCL",{ShardingKey:{"age":1,ShardingType:"range",Partition:1024}) 
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，Partition取值为空，如：
+db.testCS.createCL("testCL",{ShardingKey:{"age":1,ShardingType:"hash",Partition:""}) 
+db.testCS.createCL("testCL",{ShardingKey:{"age":1,ShardingType:"range",Partition:}) 
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:ReplSize无效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，参数格式错误，覆盖如下参数格式：
   a.引号使用错误，如字符串类型不带引号输入、bool类型带引号输入
   b.多参数
   c.为空
 如：
-db.createCL("testCS",{PageSize:"4096",Domain:domain,LobPageSize:"4096"})
-db.createCL("testCS",{PageSize:4096,Domain:"domain",LobPageSize:4096,PageSize:2048})
-db.createCL('testCS',{})
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>语法：db.collectionspace.createCL(&lt; name &gt;,[ options ])
-参数规格：
-name：string，必填，全局唯一，不能是空串，含点（.）或者美元符号（$）。且长度不超过127B。
-options:PageSize：默认为65536B，只能选填0，4096，8192，16384，32768，65536之一，0即默认为65536。非必填
-为兼容较早版本接口，db.createCL(&lt; name &gt;,[ PageSize ]) 同样可以工作。
-options:Domain，所属CS必须已经存在，且不能为 SYSDOMAIN。非必填
-options:LobPageSize，只能选填0，4096，8192，16384，32768，65536，131072，262144，524288之一，0即为默认值262144。非必填</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，覆盖name/options有效字符和边界</t>
+db.createCL("testCL",{ReplSize:4})，其中数据组节点个数为3
+db.createCL("testCL",db.createCL("testCL",{ReplSize:})
+db.createCL("testCL",db.createCL("testCL",{ReplSize:""})
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、取值非法，如test
+2、空串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:Compressed无效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入ReplSize无效取值，覆盖如下取值：
+  a.取值大于当前组内节点个数
+  b.空
+如：
+db.createCL('testCL',{ReplSize:4})，其中数据组实际节点个数为3  
+db.createCL('testCL',{ReplSize:""})
+db.createCL('testCL',{ReplSize:})
+3、检查执行结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -434,7 +599,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -456,9 +621,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -549,8 +711,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I20" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I31" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I31"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -869,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26.375" style="1" customWidth="1"/>
@@ -940,15 +1102,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="182.25" customHeight="1">
+    <row r="3" spans="1:9" ht="135">
       <c r="A3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>69</v>
+        <v>31</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
@@ -959,143 +1121,148 @@
       <c r="F3" s="4">
         <v>1</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>26</v>
+      <c r="G3" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="67.5">
+    <row r="4" spans="1:9" ht="170.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>67</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="2" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" ht="108">
+    <row r="5" spans="1:9" ht="94.5">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>24</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="1:9" ht="108">
+    <row r="6" spans="1:9" ht="94.5">
       <c r="A6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="7"/>
+        <v>25</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="2" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:9" ht="67.5">
+    <row r="7" spans="1:9" ht="94.5">
       <c r="A7" s="2" t="s">
-        <v>55</v>
+        <v>26</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9" ht="108">
+    <row r="8" spans="1:9" ht="148.5">
       <c r="A8" s="2" t="s">
-        <v>57</v>
+        <v>27</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="2" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="67.5">
+    <row r="9" spans="1:9" ht="162">
       <c r="A9" s="2" t="s">
-        <v>59</v>
+        <v>28</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9" ht="67.5">
+    <row r="10" spans="1:9" ht="94.5">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -1103,19 +1270,19 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="2" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="I10" s="4"/>
     </row>
-    <row r="11" spans="1:9" ht="67.5">
+    <row r="11" spans="1:9" ht="108">
       <c r="A11" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -1123,19 +1290,20 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="2" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" ht="135">
+    <row r="12" spans="1:9" ht="108">
       <c r="A12" s="2" t="s">
-        <v>65</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B12" s="7"/>
       <c r="C12" s="1" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -1143,19 +1311,19 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="2" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:9" ht="94.5">
+      <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" ht="189">
-      <c r="A13" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -1163,19 +1331,19 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="2" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9" ht="81">
+    <row r="14" spans="1:9" ht="94.5">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -1183,138 +1351,339 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="2" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9" ht="67.5">
+    <row r="15" spans="1:9" ht="148.5">
       <c r="A15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="4">
-        <v>1</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="2" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:9" ht="67.5">
+    <row r="16" spans="1:9" ht="94.5">
       <c r="A16" s="2" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
       </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
       <c r="G16" s="2" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="1:9" ht="94.5">
+      <c r="A17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" spans="1:9" ht="175.5">
+      <c r="A18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="1:9" ht="121.5">
+      <c r="A19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I19" s="4"/>
+    </row>
+    <row r="20" spans="1:9" ht="135">
+      <c r="A20" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I20" s="4"/>
+    </row>
+    <row r="21" spans="1:9" ht="94.5">
+      <c r="A21" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" spans="1:9" ht="94.5">
+      <c r="A22" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="4"/>
+    </row>
+    <row r="23" spans="1:9" ht="94.5">
+      <c r="A23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="4"/>
+    </row>
+    <row r="24" spans="1:9" ht="189">
+      <c r="A24" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="67.5">
-      <c r="A17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="67.5">
-      <c r="A18" s="2" t="s">
+      <c r="B24" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="I24" s="4"/>
+    </row>
+    <row r="25" spans="1:9" ht="94.5">
+      <c r="A25" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2" t="s">
+      <c r="C25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I25" s="4"/>
+    </row>
+    <row r="26" spans="1:9" ht="94.5">
+      <c r="A26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="67.5">
-      <c r="A19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="121.5">
-      <c r="A20" s="2" t="s">
+      <c r="C26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="H26" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="I26" s="4"/>
+    </row>
+    <row r="27" spans="1:9" ht="94.5">
+      <c r="A27" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="2"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="2"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="2"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="2"/>
+      <c r="C27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="94.5">
+      <c r="A28" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="94.5">
+      <c r="A29" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="94.5">
+      <c r="A30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="121.5">
+      <c r="A31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="2"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="2"/>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="2"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/参数校验/测试用例/元数据（CL）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/元数据（CL）参数校验测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="121">
   <si>
     <t>name</t>
   </si>
@@ -144,47 +144,19 @@
 2、检查执行结果</t>
   </si>
   <si>
-    <t>1、进入sdb，创建CL，输入有效的name、groups、Autosplit创建CL，如：
-db.createCL("testCL")
-2、重复步骤1，创建name相同的CL
-3、检查执行结果</t>
-  </si>
-  <si>
     <t xml:space="preserve">1、首次创建name唯一的CL，创建成功
 2、重复创建相同name的CL，创建失败，返回结果报错，并提示CL名已存在，提示信息合理准确
 </t>
   </si>
   <si>
-    <t>1、进入sdb，创建CL，输入name字符无效，覆盖如下无效取值：
-  a.包含（.）
-  b.包含$
-如：
-db.createCL('test.CL')
-db.createCL('test$CL')
-2、检查执行结果</t>
-  </si>
-  <si>
     <t>1、CL创建失败，提示参数不合法，提示信息合理准确
 2、日志打印信息合理准确</t>
   </si>
   <si>
-    <t>1、进入sdb，创建CL，输入name长度无效，覆盖如下无效取值：
-  a.空串
-  b.128字节
-如：
-db.createCL('')  或  db.createCL()   或  为128字节的有效字符
-3、检查执行结果</t>
-  </si>
-  <si>
     <t>1、CL创建失败，提示参数超出长度，提示信息合理准确
 2、日志打印信息合理准确</t>
   </si>
   <si>
-    <t>1、进入sdb，创建CL，不输入name，如：
-db.createCL({PageSize:4096,Domain:"domain"})
-2、检查执行结果</t>
-  </si>
-  <si>
     <t>1、CL创建失败，提示参数错误，提示信息合理准确
 2、日志打印信息合理准确</t>
   </si>
@@ -192,12 +164,6 @@
     <t>dropCL，删除为空和不为空的CL</t>
   </si>
   <si>
-    <t>1、进入sdb，删除为空和不为空的CL，如：
-db.dropCL("testCL_01"),其中testCL_01中存在CL
-db.dropCL("testCL_02"),其中testCL_02中不存在CL
-2、检查执行结果</t>
-  </si>
-  <si>
     <t>1、CL删除成功，db.list(4)或db.list(5)查看CL以及CL下CL已全部删除
 2、查看CL相关配置文件已删除干净</t>
   </si>
@@ -205,16 +171,6 @@
     <t>dropCL，删除不存在的CL</t>
   </si>
   <si>
-    <t>语法：db.dropCL(&lt; name &gt;)
-参数规格：
-name：string，必填，CL必须存在</t>
-  </si>
-  <si>
-    <t>1、进入sdb，删除不存在的CL，如：
-db.dropCL("testCL"),其中testCL在sdb不存在
-2、检查执行结果</t>
-  </si>
-  <si>
     <t>1、CL创建失败，提示CL不存在，提示信息合理准确
 2、日志打印信息合理准确</t>
   </si>
@@ -222,11 +178,6 @@
     <t>dropCL，删除系统CL</t>
   </si>
   <si>
-    <t>1、进入sdb，删除系统CL，如：
-db.dropCL("testCL"),其中testCL为系统CL
-2、检查执行结果</t>
-  </si>
-  <si>
     <t>1、CL创建失败，提示系统CL不能删除，提示信息合理准确
 2、日志打印信息合理准确</t>
   </si>
@@ -234,23 +185,7 @@
     <t>dropCL，指定CL名为空</t>
   </si>
   <si>
-    <t>1、进入sdb，删除CL，CL名为空，覆盖如下取值：
-db.dropCL("")
-db.dropCL()
-2、检查执行结果</t>
-  </si>
-  <si>
     <t>getCL，获取不存在的CL</t>
-  </si>
-  <si>
-    <t>语法：db.getCL(&lt; name &gt;)
-参数规格：
-name：string，必填，获取已存在的CL。不能获取系统CL。</t>
-  </si>
-  <si>
-    <t>1、进入sdb，获取指定CL，不指定CL名，如：
-db.dropCL("testCL")，其中testCL在sdb不存在
-2、检查执行结果</t>
   </si>
   <si>
     <t>1、CL获取失败，提示CL不存在，提示信息合理准确
@@ -258,12 +193,6 @@
   </si>
   <si>
     <t>getCL，指定的CL名为空</t>
-  </si>
-  <si>
-    <t>1、进入sdb，获取指定的CL，CL名为空，覆盖如下取值：
-db.getCL("")
-db.getCL()
-2、检查执行结果</t>
   </si>
   <si>
     <t>1、CL获取失败，提示参数错误，提示信息合理准确
@@ -415,13 +344,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，创建CL，输入name、options:AutoIndexId有效参数创建CL，规格如下：
-  name取任意有效值；
-  options:AutoIndexId覆盖如下取值：true|false
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>是否自动创建 _id 索引，AutoIndexId:true|false</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -512,35 +434,221 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>createCL，options:Compressed取值非bool型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:Compressed取值为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:IsMainCL取值非bool型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:IsMainCL取值为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入有效的name、groups、Autosplit创建CL，如：
+db.testCS.createCL("testCL")
+2、重复步骤1，创建name相同的CL
+3、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入name字符无效，覆盖如下无效取值：
+  a.包含（.）
+  b.包含$
+如：
+db.testCS.createCL('test.CL')
+db.testCS.createCL('test$CL')
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入name长度无效，覆盖如下无效取值：
+  a.空串
+  b.128字节
+如：
+db.testCS.createCL('')  或  db.testCS.createCL()   或  为128字节的有效字符
+3、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，不输入name，如：
+db.testCS.createCL({PageSize:4096,Domain:"domain"})
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，Compressed取值非bool型，如：
+db.testCS.createCL('testCL',{Compressed:"test"}) 
+db.testCS.createCL('testCL',{Compressed:"true"})
+3、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，Compressed取值为空，如：
+db.testCS.createCL('testCL',{Compressed:""}) 
+db.testCS.createCL('testCL',{Compressed:})
+3、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，IsMainCL取值非bool型，如：
+db.testCS.createCL('testCL',{ShardingKey:{"age":1},IsMainCL:"test"}) 
+db.testCS.createCL('testCL',{ShardingKey:{"age":1},IsMainCL:"true"})
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，IsMainCL取值为空，如：
+db.testCS.createCL('testCL',{ShardingKey:{"age":1},IsMainCL:""}) 
+db.testCS.createCL('testCL',{ShardingKey:{"age":1},IsMainCL:})
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:AutoSplit取值为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:AutoIndexId取值非bool型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:AutoIndexId取值为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，AutoIndexId取值非bool型，如：
+db.testCS.createCL("testCL",{ShardingKey:{"age":1},ShardingType:"hash",AutoIndexId:"test"} 
+db.testCS.createCL("testCL",{ShardingKey:{"age":1},ShardingType:"hash",AutoIndexId:"true"})
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入name、options:AutoIndexId有效参数创建CL，规格如下：
+  name取任意有效值；
+  options:AutoIndexId覆盖如下取值：true|false
+如：db.testCS.createCL("testCL",{ShardingKey:{"age":1},ShardingType:"hash",AutoIndexId:false})
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，AutoIndexId取值为空，如：
+db.testCS.createCL("testCL",{ShardingKey:{"age":1},ShardingType:"hash",AutoIndexId:""}) 
+db.testCS.createCL("testCL",{ShardingKey:{"age":1},ShardingType:"hash",AutoIndexId:})
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:Group取值为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:AutoSplit无效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，AutoSplit无效取值，如：
+db.testCS.createCL("testCL",{ShardingKey:{"age":1},ShardingType:"hash",AutoSplit:"test"}) 
+db.testCS.createCL("testCL",{ShardingKey:{"age":1},ShardingType:"hash",AutoSplit:"true"})
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，IsMainCL取值为空，如：
+db.testCS.createCL("testCL",{ShardingKey:{"age":1},ShardingType:"hash",AutoSplit:""}) 
+db.testCS.createCL("testCL",{ShardingKey:{"age":1},ShardingType:"hash",AutoSplit:})
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入ReplSize无效取值，覆盖如下取值：
+  a.取值大于当前组内节点个数
+  b.空
+如：
+db.testCS.createCL('testCL',{ReplSize:4})，其中数据组实际节点个数为3  
+db.testCS.createCL('testCL',{ReplSize:""})
+db.testCS.createCL('testCL',{ReplSize:})
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，options:Group指定的组在对应的CS所属域中不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Group必须存在于集合空间所属的域中（所有复制组均属于SYSDOMAIN，即如果集合空间没有指定域，则系统内任意复制组均可）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，指定的组在对应的CS（指定域，域中有指定组group1）所属域中不存在，如：
+db.testCS.createCL("testCL",{Group:"group3"})，其中group3在testCS所属域中不存在
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，Group取值为空，如：
+db.testCS.createCL("testCL",{Group:""}) 
+db.testCS.createCL("testCL",{Group:})
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1、进入sdb，创建CL，参数格式错误，覆盖如下参数格式：
   a.引号使用错误，如字符串类型不带引号输入、bool类型带引号输入
   b.多参数
   c.为空
 如：
-db.createCL("testCL",{ReplSize:4})，其中数据组节点个数为3
-db.createCL("testCL",db.createCL("testCL",{ReplSize:})
-db.createCL("testCL",db.createCL("testCL",{ReplSize:""})
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、取值非法，如test
-2、空串</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，options:Compressed无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CL，输入ReplSize无效取值，覆盖如下取值：
-  a.取值大于当前组内节点个数
-  b.空
-如：
-db.createCL('testCL',{ReplSize:4})，其中数据组实际节点个数为3  
-db.createCL('testCL',{ReplSize:""})
-db.createCL('testCL',{ReplSize:})
-3、检查执行结果</t>
+db.testCS.createCL(testCL,{ShardingKey:{age:1},ShardingType:hash,AutoIndexId:"false"})
+db.testCS.createCL("testCL",test:true})
+db.testCS.createCL({})
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，删除不存在的CL，如：
+db.testCS.dropCL("testCL"),其中testCL在sdb不存在
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，删除系统CL，如：
+db.testCS.dropCL("testCL"),其中testCL为系统CL
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，删除CL，CL名为空，覆盖如下取值：
+db.testCS.dropCL("")
+db.testCS.dropCL()
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，删除为空和不为空的CL，如：
+db.testCS.dropCL("testCL_01"),其中testCL_01中存在数据
+db.testCS.dropCL("testCL_02"),其中testCL_02中不存在数据
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：db.collectionspace.dropCL(&lt; name &gt;)
+参数规格：
+name：string，必填，CL必须存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：db.collectionspace.getCL(&lt; name &gt;)
+参数规格：
+name：string，必填，获取已存在的CL。不能获取系统CL。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，获取指定CL，不指定CL名，如：
+db.testCS.dropCL("testCL")，其中testCL在sdb不存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，获取指定的CL，CL名为空，覆盖如下取值：
+db.collectionspace.getCL("")
+db.collectionspace.getCL()
+2、检查执行结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -711,8 +819,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I31" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I38" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I38"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1031,14 +1139,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="30" style="5" customWidth="1"/>
     <col min="3" max="3" width="22.25" style="1" customWidth="1"/>
     <col min="4" max="6" width="5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="41" style="1" customWidth="1"/>
+    <col min="7" max="7" width="44.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="34" style="1" customWidth="1"/>
     <col min="9" max="9" width="40.75" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
@@ -1110,7 +1218,7 @@
         <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
@@ -1125,7 +1233,7 @@
         <v>32</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -1133,22 +1241,22 @@
     </row>
     <row r="4" spans="1:9" ht="170.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -1160,16 +1268,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="2" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -1178,19 +1286,19 @@
         <v>25</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="2" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -1199,19 +1307,19 @@
         <v>26</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -1223,16 +1331,16 @@
         <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="I8" s="4"/>
     </row>
@@ -1241,19 +1349,19 @@
         <v>28</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="2" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="I9" s="4"/>
     </row>
@@ -1262,7 +1370,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -1270,10 +1378,10 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="I10" s="4"/>
     </row>
@@ -1282,7 +1390,7 @@
         <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -1290,20 +1398,20 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="2" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" ht="108">
+    <row r="12" spans="1:9" ht="121.5">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -1311,10 +1419,10 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="2" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I12" s="4"/>
     </row>
@@ -1323,7 +1431,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -1331,19 +1439,19 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="2" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="94.5">
       <c r="A14" s="2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -1351,37 +1459,37 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="148.5">
       <c r="A15" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="2" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="94.5">
       <c r="A16" s="2" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -1389,37 +1497,37 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="94.5">
       <c r="A17" s="2" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="175.5">
       <c r="A18" s="2" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -1427,19 +1535,19 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="121.5">
       <c r="A19" s="2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D19" s="4">
         <v>1</v>
@@ -1447,19 +1555,19 @@
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="135">
       <c r="A20" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D20" s="4">
         <v>1</v>
@@ -1467,223 +1575,361 @@
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="94.5">
       <c r="A21" s="2" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
+      <c r="G21" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" ht="94.5">
       <c r="A22" s="2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="94.5">
       <c r="A23" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
+      <c r="G23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="189">
+    <row r="24" spans="1:9" ht="94.5">
       <c r="A24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="94.5">
+    <row r="25" spans="1:9" ht="108">
       <c r="A25" s="2" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="4">
-        <v>1</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="2" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="94.5">
       <c r="A26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="2" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" ht="94.5">
       <c r="A27" s="2" t="s">
-        <v>48</v>
+        <v>108</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
       <c r="G27" s="2" t="s">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>50</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" ht="94.5">
       <c r="A28" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I28" s="4"/>
+    </row>
+    <row r="29" spans="1:9" ht="121.5">
+      <c r="A29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I29" s="4"/>
+    </row>
+    <row r="30" spans="1:9" ht="121.5">
+      <c r="A30" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I30" s="4"/>
+    </row>
+    <row r="31" spans="1:9" ht="162">
+      <c r="A31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I31" s="4"/>
+    </row>
+    <row r="32" spans="1:9" ht="94.5">
+      <c r="A32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" s="4">
+        <v>1</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I32" s="4"/>
+    </row>
+    <row r="33" spans="1:9" ht="94.5">
+      <c r="A33" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I33" s="4"/>
+    </row>
+    <row r="34" spans="1:9" ht="94.5">
+      <c r="A34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="94.5">
+      <c r="A35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" s="4">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="94.5">
+      <c r="A36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="94.5">
+      <c r="A37" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37" s="4">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="121.5">
+      <c r="A38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" s="4">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="4">
-        <v>1</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="94.5">
-      <c r="A29" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="94.5">
-      <c r="A30" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="121.5">
-      <c r="A31" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" s="4">
-        <v>1</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="2"/>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="2"/>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="2"/>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="2"/>
+      <c r="H38" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="2"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="2"/>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="2"/>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/参数校验/测试用例/元数据（CL）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/元数据（CL）参数校验测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="122">
   <si>
     <t>name</t>
   </si>
@@ -171,15 +171,7 @@
     <t>dropCL，删除不存在的CL</t>
   </si>
   <si>
-    <t>1、CL创建失败，提示CL不存在，提示信息合理准确
-2、日志打印信息合理准确</t>
-  </si>
-  <si>
     <t>dropCL，删除系统CL</t>
-  </si>
-  <si>
-    <t>1、CL创建失败，提示系统CL不能删除，提示信息合理准确
-2、日志打印信息合理准确</t>
   </si>
   <si>
     <t>dropCL，指定CL名为空</t>
@@ -649,6 +641,21 @@
 db.collectionspace.getCL("")
 db.collectionspace.getCL()
 2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CL删除失败，提示CL不存在，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CL删除失败，提示系统CL不能删除，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CL删除失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1218,7 +1225,7 @@
         <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
@@ -1233,7 +1240,7 @@
         <v>32</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -1241,22 +1248,22 @@
     </row>
     <row r="4" spans="1:9" ht="170.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -1268,16 +1275,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -1286,19 +1293,19 @@
         <v>25</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -1307,19 +1314,19 @@
         <v>26</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -1331,16 +1338,16 @@
         <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I8" s="4"/>
     </row>
@@ -1349,19 +1356,19 @@
         <v>28</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I9" s="4"/>
     </row>
@@ -1370,7 +1377,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -1378,7 +1385,7 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>33</v>
@@ -1390,7 +1397,7 @@
         <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -1398,7 +1405,7 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>34</v>
@@ -1411,7 +1418,7 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -1419,7 +1426,7 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>35</v>
@@ -1431,7 +1438,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -1439,7 +1446,7 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>36</v>
@@ -1448,10 +1455,10 @@
     </row>
     <row r="14" spans="1:9" ht="94.5">
       <c r="A14" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -1459,25 +1466,25 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>36</v>
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9" ht="148.5">
+    <row r="15" spans="1:9" ht="135">
       <c r="A15" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>36</v>
@@ -1486,10 +1493,10 @@
     </row>
     <row r="16" spans="1:9" ht="94.5">
       <c r="A16" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -1497,7 +1504,7 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>36</v>
@@ -1506,28 +1513,28 @@
     </row>
     <row r="17" spans="1:9" ht="94.5">
       <c r="A17" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>36</v>
       </c>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="175.5">
+    <row r="18" spans="1:9" ht="162">
       <c r="A18" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -1535,19 +1542,19 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="121.5">
+    <row r="19" spans="1:9" ht="94.5">
       <c r="A19" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D19" s="4">
         <v>1</v>
@@ -1555,7 +1562,7 @@
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>36</v>
@@ -1564,10 +1571,10 @@
     </row>
     <row r="20" spans="1:9" ht="135">
       <c r="A20" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D20" s="4">
         <v>1</v>
@@ -1575,7 +1582,7 @@
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>36</v>
@@ -1584,16 +1591,16 @@
     </row>
     <row r="21" spans="1:9" ht="94.5">
       <c r="A21" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>36</v>
@@ -1602,16 +1609,16 @@
     </row>
     <row r="22" spans="1:9" ht="94.5">
       <c r="A22" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>36</v>
@@ -1620,16 +1627,16 @@
     </row>
     <row r="23" spans="1:9" ht="94.5">
       <c r="A23" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>36</v>
@@ -1638,16 +1645,16 @@
     </row>
     <row r="24" spans="1:9" ht="94.5">
       <c r="A24" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>36</v>
@@ -1656,16 +1663,16 @@
     </row>
     <row r="25" spans="1:9" ht="108">
       <c r="A25" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>36</v>
@@ -1674,16 +1681,16 @@
     </row>
     <row r="26" spans="1:9" ht="94.5">
       <c r="A26" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>36</v>
@@ -1692,19 +1699,19 @@
     </row>
     <row r="27" spans="1:9" ht="94.5">
       <c r="A27" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>36</v>
@@ -1713,16 +1720,16 @@
     </row>
     <row r="28" spans="1:9" ht="94.5">
       <c r="A28" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>36</v>
@@ -1731,34 +1738,34 @@
     </row>
     <row r="29" spans="1:9" ht="121.5">
       <c r="A29" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>36</v>
       </c>
       <c r="I29" s="4"/>
     </row>
-    <row r="30" spans="1:9" ht="121.5">
+    <row r="30" spans="1:9" ht="94.5">
       <c r="A30" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>36</v>
@@ -1770,7 +1777,7 @@
         <v>22</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D31" s="4">
         <v>1</v>
@@ -1778,7 +1785,7 @@
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>36</v>
@@ -1790,7 +1797,7 @@
         <v>37</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D32" s="4">
         <v>1</v>
@@ -1798,7 +1805,7 @@
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>38</v>
@@ -1810,10 +1817,10 @@
         <v>39</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D33" s="4">
         <v>1</v>
@@ -1821,102 +1828,102 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>40</v>
+        <v>119</v>
       </c>
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" ht="94.5">
       <c r="A34" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D34" s="4">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>42</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="94.5">
       <c r="A35" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D35" s="4">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="94.5">
       <c r="A36" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D36" s="4">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="94.5">
       <c r="A37" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D37" s="4">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="121.5">
       <c r="A38" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D38" s="4">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D38" s="4">
-        <v>1</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="H38" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:9">

--- a/internal_doc/05.测试设计/参数校验/测试用例/元数据（CL）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/元数据（CL）参数校验测试用例.xlsx
@@ -13,6 +13,61 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+添加</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>alter</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>相关用例</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <connection id="1" name="testcase" type="4" refreshedVersion="0" background="1">
@@ -22,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="153">
   <si>
     <t>name</t>
   </si>
@@ -79,48 +134,6 @@
   </si>
   <si>
     <t>测试用例摘要（测试目的）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，name重复</t>
-  </si>
-  <si>
-    <t>createCL，name字符无效</t>
-  </si>
-  <si>
-    <t>createCL，name长度无效</t>
-  </si>
-  <si>
-    <t>createCL，name参数不存在</t>
-  </si>
-  <si>
-    <t>createCL，格式错误</t>
-  </si>
-  <si>
-    <t>语法：db.collectionspace.createCL(&lt; name &gt;,[ options ])
-参数规格：
-name：string，必填，全局唯一，不能是空串，含点（.）或者美元符号（$）。且长度不超过127B。
-options，非必填</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，覆盖options:ReplSize有效字符和边界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，覆盖options:Compressed有效字符和边界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，覆盖options:IsMainCL有效字符和边界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，覆盖options:Group有效字符和边界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，覆盖options:AutoIndexId有效字符和边界</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -130,10 +143,6 @@
   </si>
   <si>
     <t>Group必须存在于集合空间所属的域中（所有复制组均属于SYSDOMAIN，即如果集合空间没有指定域，则系统内任意复制组均可）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，覆盖name有效字符和边界</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -161,44 +170,19 @@
 2、日志打印信息合理准确</t>
   </si>
   <si>
-    <t>dropCL，删除为空和不为空的CL</t>
-  </si>
-  <si>
     <t>1、CL删除成功，db.list(4)或db.list(5)查看CL以及CL下CL已全部删除
 2、查看CL相关配置文件已删除干净</t>
   </si>
   <si>
-    <t>dropCL，删除不存在的CL</t>
-  </si>
-  <si>
-    <t>dropCL，删除系统CL</t>
-  </si>
-  <si>
-    <t>dropCL，指定CL名为空</t>
-  </si>
-  <si>
-    <t>getCL，获取不存在的CL</t>
-  </si>
-  <si>
     <t>1、CL获取失败，提示CL不存在，提示信息合理准确
 2、日志打印信息合理准确</t>
   </si>
   <si>
-    <t>getCL，指定的CL名为空</t>
-  </si>
-  <si>
     <t>1、CL获取失败，提示参数错误，提示信息合理准确
 2、日志打印信息合理准确</t>
   </si>
   <si>
     <t>1、CL获取成功，指定的CL被直接忽略，返回结果显示所有CL（非系统CL）</t>
-  </si>
-  <si>
-    <t>listCollections，加条件查询</t>
-  </si>
-  <si>
-    <t>语法：db.listCollections()
-无参数</t>
   </si>
   <si>
     <t>1、进入sdb，获取所有CL（非系统CL），指定CL名，覆盖如下取值：
@@ -226,10 +210,6 @@
 2、sdb已存在数据组group1、group2、group3
 3、sdb已存在域domain，该域有指定多个组
 4、sdb已存在testCS，且指定域为domian</t>
-  </si>
-  <si>
-    <t>createCL，覆盖options:ShardingKey/ShardingType/Partition/AutoSplit有效字符和边界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>options:ShardingKey
@@ -322,15 +302,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，创建CL，输入name、options:GroupL有效参数创建CL，规格如下：
-name取任意有效值；
-options:Group覆盖如下取值：
-  a.所属CS指定域，指定CL的Group为CS所属域中的group
-  b.所属CS不指定域，指定CL的Group为系统内任意复制组
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、CL创建成功，执行db.listCollections或db.snapshot可以查看到新创建的CL。检查CL关联的组为创建CL时指定的组。
 2、插入数据，数据全部落到指定组</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -343,14 +314,6 @@
     <t>1、CL创建成功，执行db.listCollections或db.snapshot可以查看到新创建的CL。
 2、配置AutoIndexId为true则自动创建 _id 索引，执行db.collectionspace.collection.listIndexes()查看有_id索引，索引创建正确；
 配置AutoIndexId为false则不自动创建 _id 索引，执行db.collectionspace.collection.listIndexes()查看没有_id索引。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，options:ShardingKey无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，options:ShardingKey为空串</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -358,14 +321,6 @@
 db.testCS.createCL("testCL",{ShardingKey:{"age":0}}  
 db.testCS.createCL("testCL",{ShardingKey:{"age":"-1"}} 
 3、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，options:ShardingType为空串</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，options:ShardingType取值非bool型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -385,10 +340,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>createCL，options:Partition无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，创建CL，输入ShardingKey为空串，如：
 db.testCS.createCL("testCL",{ShardingKey:{"age":1,ShardingType:""}) 
 db.testCS.createCL("testCL",{ShardingKey:{"age":1,ShardingType:}}) 
@@ -396,22 +347,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>createCL，options:Partition取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、CL创建失败，提示参数错误，提示信息合理准确
 2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CL，Partition无效取值，覆盖如下取值：
-  a.取值为：4(2^2)、2097152（2^21）、7、1048577
-  b.range分区，Partition取有效值，如1024
-如：
-db.testCS.createCL("testCL",{ShardingKey:{"age":1,ShardingType:"hash",Partition:4}) 
-db.testCS.createCL("testCL",{ShardingKey:{"age":1,ShardingType:"range",Partition:1024}) 
-2、检查执行结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -419,26 +356,6 @@
 db.testCS.createCL("testCL",{ShardingKey:{"age":1,ShardingType:"hash",Partition:""}) 
 db.testCS.createCL("testCL",{ShardingKey:{"age":1,ShardingType:"range",Partition:}) 
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，options:ReplSize无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，options:Compressed取值非bool型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，options:Compressed取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，options:IsMainCL取值非bool型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，options:IsMainCL取值为空</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -496,18 +413,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>createCL，options:AutoSplit取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，options:AutoIndexId取值非bool型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，options:AutoIndexId取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，创建CL，AutoIndexId取值非bool型，如：
 db.testCS.createCL("testCL",{ShardingKey:{"age":1},ShardingType:"hash",AutoIndexId:"test"} 
 db.testCS.createCL("testCL",{ShardingKey:{"age":1},ShardingType:"hash",AutoIndexId:"true"})
@@ -527,14 +432,6 @@
 db.testCS.createCL("testCL",{ShardingKey:{"age":1},ShardingType:"hash",AutoIndexId:""}) 
 db.testCS.createCL("testCL",{ShardingKey:{"age":1},ShardingType:"hash",AutoIndexId:})
 3、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，options:Group取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL，options:AutoSplit无效取值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -563,10 +460,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>createCL，options:Group指定的组在对应的CS所属域中不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Group必须存在于集合空间所属的域中（所有复制组均属于SYSDOMAIN，即如果集合空间没有指定域，则系统内任意复制组均可）。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -658,12 +551,374 @@
 2、日志打印信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>1、进入sdb，创建CL，输入name、options:GroupL有效参数创建CL，规格如下：
+name取任意有效值；
+options:Group覆盖如下取值：
+  a.所属CS指定域，指定CL的Group为CS所属域中的group
+  b.所属CS不指定域，指定CL的Group为系统内任意复制组
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL，Partition无效取值，覆盖如下取值：
+  a.取值为：4(2^2)、2097152（2^21）、7、1048577
+  b.range分区，Partition取有效值，如1024
+如：
+db.testCS.createCL("testCL",{ShardingKey:{"age":1,ShardingType:"hash",Partition:4}) 
+db.testCS.createCL("testCL",{ShardingKey:{"age":1,ShardingType:"range",Partition:1024}) 
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，在指定CS创建CL，该CS所在域没有指定AutoSplit，创建该CL时也不指定AutoSplit
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CL创建成功，执行db.listCollections或db.snapshot可以查看到新创建的CL。该CL不是自动切分表，查看该CL的AutoSplit属性为false</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：db.listCollections()
+无参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：db.collectionspace.createCL(&lt; name &gt;,[ options ])
+参数规格：
+name：string，必填，全局唯一，不能是空串，含点（.）或者美元符号（$）。且长度不超过127B。
+options，非必填</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，修改CL，修改options:ReplSize有效，覆盖如下取值：
+  options:ReplSize覆盖如下取值：0、-1（当前活动的节点）、7、取值等于数据组节点个数
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、CL修改成功，执行db.listCollections或db.snapshot可以查看到CL的ReplSize属性已更新。
+2、在CL插入批量数据，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>检查写数据按创建CL是设置的ReplSize返回结果</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，修改CL，输入ReplSize无效取值，覆盖如下取值：
+  a.取值大于当前组内节点个数
+  b.空
+如：
+db.testCS.createCL.alter({ReplSize:4})，其中数据组实际节点个数为3  
+db.testCS.createCL.alter({ReplSize:""})
+db.testCS.createCL.alter({ReplSize:})
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">语法：db.collectionspace.collection.alter(&lt;options&gt;)
+参数规格（同createCL）：
+ReplSize/ShardingKey/ShardingType/Partition
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>分区集合不能修改与分区相关的属性。
+修改为分区集合后需要手动进行 split</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在数据组group1、group2、group3
+3、sdb已存在域domain
+4、sdb已存在testCS.testCL，且testCS指定域为domian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在数据组group1、group2、group3
+3、sdb已存在域domain
+4、sdb已存在testCS.testCL，且testCS指定域为domian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、CL修改成功，执行db.listCollections或db.snapshot可以查看到CL的options:ShardingKey/ShardingType/Partition属性已更新。
+2、在CL插入批量数据，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>检查写数据按新的分区键/分区类型/区间存放数据</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CL修改失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">分区集合不能修改与分区相关的属性。
+修改为分区集合后需要手动进行 split
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，修改CL（该CL不是分区集合），输入options:ShardingKey/ShardingType/AutoSplit有效参数，覆盖如下取值：
+options:ShardingKey覆盖如下取值：
+  a.单分区键，取值1|-1
+  b.多分区键，取值1|-1
+options:ShardingType覆盖如下取值：
+  a.ShardingType:"hash"
+  b.ShardingType:"range"
+options:Partition覆盖如下取值：
+  a.hash分区，有效取值：8、1048576
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，修改CL（该CL不是分区集合），输入ShardingKey无效取值，如：
+db.testCS.testCL.alter({ShardingKey:{"age":0}}  
+db.testCS.createCL.alter({ShardingKey:{"age":"-1"}} 
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，修改CL（该CL不是分区集合），输入ShardingKey为空串，如：
+db.testCS.createCL.alter({ShardingKey:{"age":""}}) 
+db.testCS.createCL.alter({ShardingKey:{"age":}})
+db.testCS.createCL.alter({ShardingKey:{}})  
+db.testCS.createCL.alter({ShardingKey:}) 
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，修改CL（该CL不是分区集合），输入ShardingType取值非bool型，如：
+db.testCS.createCL.alter({ShardingKey:{"age":"test"}})   
+db.testCS.createCL.alter({ShardingKey:{"age":"Y"}})  
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，修改CL（该CL不是分区集合），Partition无效取值，覆盖如下取值：
+  a.取值为：4(2^2)、2097152（2^21）、7、1048577
+  b.range分区，Partition取有效值，如1024
+如：
+db.testCS.createCL.alter({ShardingKey:{"age":1,ShardingType:"hash",Partition:4}) 
+db.testCS.createCL.alter({ShardingKey:{"age":1,ShardingType:"range",Partition:1024}) 
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，修改CL（该CL不是分区集合），Partition取值为空，如：
+db.testCS.createCL.alter({ShardingKey:{"age":1,ShardingType:"hash",Partition:""}) 
+db.testCS.createCL.alter({ShardingKey:{"age":1,ShardingType:"range",Partition:}) 
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CL（该CL不是分区集合），输入ShardingKey为空串，如：
+db.testCS.createCL("testCL",{ShardingKey:{"age":1,ShardingType:""}) 
+db.testCS.createCL("testCL",{ShardingKey:{"age":1,ShardingType:}}) 
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，修改CL（该CL为分区集合），修改分区集合的options:ShardingKey/ShardingType/Partition属性，输入值有效，如：
+db.testCS.createCL.alter({ShardingKey:{a:1},ShardingType:"hash",Partition:1024})
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CL修改失败，提示分区集合不允许修改ShardingKey/ShardingType/Partition属性，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL，覆盖name有效字符和边界_st.verify.CL.001</t>
+  </si>
+  <si>
+    <t>createCL，覆盖options:ShardingKey/ShardingType/Partition/AutoSplit有效字符和边界_st.verify.CL.002</t>
+  </si>
+  <si>
+    <t>createCL，覆盖options:ReplSize有效边界_st.verify.CL.003</t>
+  </si>
+  <si>
+    <t>createCL，覆盖options:Compressed有效字符和边界_st.verify.CL.004</t>
+  </si>
+  <si>
+    <t>createCL，覆盖options:IsMainCL有效字符和边界_st.verify.CL.005</t>
+  </si>
+  <si>
+    <t>createCL，覆盖options:Group有效字符和边界_st.verify.CL.006</t>
+  </si>
+  <si>
+    <t>createCL，覆盖options:AutoIndexId有效字符和边界_st.verify.CL.007</t>
+  </si>
+  <si>
+    <t>createCL，name重复_st.verify.CL.008</t>
+  </si>
+  <si>
+    <t>createCL，name字符无效_st.verify.CL.009</t>
+  </si>
+  <si>
+    <t>createCL，name长度无效_st.verify.CL.010</t>
+  </si>
+  <si>
+    <t>createCL，name参数不存在_st.verify.CL.011</t>
+  </si>
+  <si>
+    <t>createCL，options:ShardingKey无效取值_st.verify.CL.012</t>
+  </si>
+  <si>
+    <t>createCL，options:ShardingKey为空串_st.verify.CL.013</t>
+  </si>
+  <si>
+    <t>createCL，options:ShardingType取值非bool型_st.verify.CL.014</t>
+  </si>
+  <si>
+    <t>createCL，options:ShardingType为空串_st.verify.CL.015</t>
+  </si>
+  <si>
+    <t>createCL，options:Partition无效取值_st.verify.CL.016</t>
+  </si>
+  <si>
+    <t>createCL，options:Partition取值为空_st.verify.CL.017</t>
+  </si>
+  <si>
+    <t>createCL，options:ReplSize无效取值_st.verify.CL.018</t>
+  </si>
+  <si>
+    <t>createCL，options:Compressed取值非bool型_st.verify.CL.019</t>
+  </si>
+  <si>
+    <t>createCL，options:Compressed取值为空_st.verify.CL.020</t>
+  </si>
+  <si>
+    <t>createCL，options:IsMainCL取值非bool型_st.verify.CL.021</t>
+  </si>
+  <si>
+    <t>createCL，options:IsMainCL取值为空_st.verify.CL.022</t>
+  </si>
+  <si>
+    <t>createCL，options:AutoSplit无效取值_st.verify.CL.023</t>
+  </si>
+  <si>
+    <t>createCL，options:AutoSplit取值为空_st.verify.CL.024</t>
+  </si>
+  <si>
+    <t>createCL，options:Group指定的组在对应的CS所属域中不存在_st.verify.CL.025</t>
+  </si>
+  <si>
+    <t>createCL，options:Group取值为空_st.verify.CL.026</t>
+  </si>
+  <si>
+    <t>createCL，options:AutoIndexId取值非bool型_st.verify.CL.027</t>
+  </si>
+  <si>
+    <t>createCL，options:AutoIndexId取值为空_st.verify.CL.028</t>
+  </si>
+  <si>
+    <t>createCL，格式错误_st.verify.CL.029</t>
+  </si>
+  <si>
+    <t>dropCL，删除为空和不为空的CL_st.verify.CL.030</t>
+  </si>
+  <si>
+    <t>dropCL，删除不存在的CL_st.verify.CL.031</t>
+  </si>
+  <si>
+    <t>dropCL，删除系统CL_st.verify.CL.032</t>
+  </si>
+  <si>
+    <t>dropCL，指定CL名为空_st.verify.CL.033</t>
+  </si>
+  <si>
+    <t>getCL，获取不存在的CL_st.verify.CL.034</t>
+  </si>
+  <si>
+    <t>getCL，指定的CL名为空_st.verify.CL.035</t>
+  </si>
+  <si>
+    <t>listCollections，加条件查询_st.verify.CL.036</t>
+  </si>
+  <si>
+    <t>创建CL时所在CS所属Domain不指定自动切分，不指定AutoSplit创建CL_st.verify.CL.037</t>
+  </si>
+  <si>
+    <t>alter，覆盖options:ReplSize有效边界_st.verify.CL.038</t>
+  </si>
+  <si>
+    <t>alter，options:ReplSize无效取值_st.verify.CL.039</t>
+  </si>
+  <si>
+    <t>alter，覆盖options:ShardingKey/ShardingType/Partition有效字符和边界_st.verify.CL.040</t>
+  </si>
+  <si>
+    <t>alter，options:ShardingKey无效取值_st.verify.CL.041</t>
+  </si>
+  <si>
+    <t>alter，options:ShardingKey为空串_st.verify.CL.042</t>
+  </si>
+  <si>
+    <t>alter，options:ShardingType取值非bool型_st.verify.CL.043</t>
+  </si>
+  <si>
+    <t>alter，options:ShardingType为空串_st.verify.CL.044</t>
+  </si>
+  <si>
+    <t>alter，options:Partition无效取值_st.verify.CL.045</t>
+  </si>
+  <si>
+    <t>alter，options:Partition取值为空_st.verify.CL.046</t>
+  </si>
+  <si>
+    <t>alter，修改分区集合的options:ShardingKey/ShardingType/Partition属性_st.verify.CL.047</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -689,6 +944,27 @@
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -826,8 +1102,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I38" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I49" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I49"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1146,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26.375" style="1" customWidth="1"/>
@@ -1155,7 +1431,7 @@
     <col min="4" max="6" width="5" style="1" customWidth="1"/>
     <col min="7" max="7" width="44.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="34" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.125" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1219,28 +1495,28 @@
     </row>
     <row r="3" spans="1:9" ht="135">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
       </c>
       <c r="E3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="4">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -1248,702 +1524,1241 @@
     </row>
     <row r="4" spans="1:9" ht="170.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
       <c r="G4" s="2" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="94.5">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
       <c r="G5" s="2" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I5" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="94.5">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
       <c r="G6" s="2" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="94.5">
       <c r="A7" s="2" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
       <c r="G7" s="2" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="148.5">
       <c r="A8" s="2" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
       <c r="G8" s="2" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I8" s="4"/>
+        <v>44</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="162">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
       <c r="G9" s="2" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I9" s="4"/>
+        <v>46</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="94.5">
       <c r="A10" s="2" t="s">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
       <c r="G10" s="2" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="108">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="E11" s="4">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1</v>
+      </c>
       <c r="G11" s="2" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="121.5">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="E12" s="4">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1</v>
+      </c>
       <c r="G12" s="2" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="94.5">
       <c r="A13" s="2" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="E13" s="4">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
       <c r="G13" s="2" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="94.5">
       <c r="A14" s="2" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
       <c r="G14" s="2" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I14" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="135">
       <c r="A15" s="2" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1</v>
+      </c>
       <c r="G15" s="2" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I15" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="94.5">
       <c r="A16" s="2" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="E16" s="4">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
       <c r="G16" s="2" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="94.5">
       <c r="A17" s="2" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1</v>
+      </c>
       <c r="G17" s="2" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I17" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:9" ht="162">
       <c r="A18" s="2" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I18" s="4"/>
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:9" ht="94.5">
       <c r="A19" s="2" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D19" s="4">
         <v>1</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="E19" s="4">
+        <v>2</v>
+      </c>
+      <c r="F19" s="4">
+        <v>1</v>
+      </c>
       <c r="G19" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I19" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:9" ht="135">
       <c r="A20" s="2" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D20" s="4">
         <v>1</v>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="E20" s="4">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4">
+        <v>1</v>
+      </c>
       <c r="G20" s="2" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I20" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:9" ht="94.5">
       <c r="A21" s="2" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4">
+        <v>1</v>
+      </c>
       <c r="G21" s="2" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I21" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I21" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:9" ht="94.5">
       <c r="A22" s="2" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4">
+        <v>2</v>
+      </c>
+      <c r="F22" s="4">
+        <v>1</v>
+      </c>
       <c r="G22" s="2" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I22" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I22" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:9" ht="94.5">
       <c r="A23" s="2" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4">
+        <v>2</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1</v>
+      </c>
       <c r="G23" s="2" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I23" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I23" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:9" ht="94.5">
       <c r="A24" s="2" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4">
+        <v>2</v>
+      </c>
+      <c r="F24" s="4">
+        <v>1</v>
+      </c>
       <c r="G24" s="2" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I24" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I24" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:9" ht="108">
       <c r="A25" s="2" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4">
+        <v>2</v>
+      </c>
+      <c r="F25" s="4">
+        <v>1</v>
+      </c>
       <c r="G25" s="2" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I25" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I25" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:9" ht="94.5">
       <c r="A26" s="2" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4">
+        <v>2</v>
+      </c>
+      <c r="F26" s="4">
+        <v>1</v>
+      </c>
       <c r="G26" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I26" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I26" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:9" ht="94.5">
       <c r="A27" s="2" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4">
+        <v>2</v>
+      </c>
+      <c r="F27" s="4">
+        <v>1</v>
+      </c>
       <c r="G27" s="2" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I27" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I27" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:9" ht="94.5">
       <c r="A28" s="2" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4">
+        <v>2</v>
+      </c>
+      <c r="F28" s="4">
+        <v>1</v>
+      </c>
       <c r="G28" s="2" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I28" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I28" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:9" ht="121.5">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4">
+        <v>2</v>
+      </c>
+      <c r="F29" s="4">
+        <v>1</v>
+      </c>
       <c r="G29" s="2" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I29" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:9" ht="94.5">
       <c r="A30" s="2" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4">
+        <v>2</v>
+      </c>
+      <c r="F30" s="4">
+        <v>1</v>
+      </c>
       <c r="G30" s="2" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I30" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I30" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:9" ht="162">
       <c r="A31" s="2" t="s">
-        <v>22</v>
+        <v>134</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D31" s="4">
         <v>1</v>
       </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
+      <c r="E31" s="4">
+        <v>2</v>
+      </c>
+      <c r="F31" s="4">
+        <v>1</v>
+      </c>
       <c r="G31" s="2" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I31" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I31" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:9" ht="94.5">
       <c r="A32" s="2" t="s">
-        <v>37</v>
+        <v>135</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D32" s="4">
         <v>1</v>
       </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
+      <c r="E32" s="4">
+        <v>2</v>
+      </c>
+      <c r="F32" s="4">
+        <v>1</v>
+      </c>
       <c r="G32" s="2" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I32" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="I32" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:9" ht="94.5">
       <c r="A33" s="2" t="s">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D33" s="4">
         <v>1</v>
       </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
+      <c r="E33" s="4">
+        <v>2</v>
+      </c>
+      <c r="F33" s="4">
+        <v>1</v>
+      </c>
       <c r="G33" s="2" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I33" s="4"/>
+        <v>79</v>
+      </c>
+      <c r="I33" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:9" ht="94.5">
       <c r="A34" s="2" t="s">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D34" s="4">
         <v>1</v>
       </c>
+      <c r="E34" s="4">
+        <v>2</v>
+      </c>
+      <c r="F34" s="4">
+        <v>1</v>
+      </c>
       <c r="G34" s="2" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>120</v>
+        <v>80</v>
+      </c>
+      <c r="I34" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="94.5">
       <c r="A35" s="2" t="s">
-        <v>41</v>
+        <v>138</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D35" s="4">
         <v>1</v>
       </c>
+      <c r="E35" s="4">
+        <v>2</v>
+      </c>
+      <c r="F35" s="4">
+        <v>1</v>
+      </c>
       <c r="G35" s="2" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>121</v>
+        <v>81</v>
+      </c>
+      <c r="I35" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="94.5">
       <c r="A36" s="2" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D36" s="4">
         <v>1</v>
       </c>
+      <c r="E36" s="4">
+        <v>2</v>
+      </c>
+      <c r="F36" s="4">
+        <v>1</v>
+      </c>
       <c r="G36" s="2" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
+      </c>
+      <c r="I36" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="94.5">
       <c r="A37" s="2" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D37" s="4">
         <v>1</v>
       </c>
+      <c r="E37" s="4">
+        <v>2</v>
+      </c>
+      <c r="F37" s="4">
+        <v>1</v>
+      </c>
       <c r="G37" s="2" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>45</v>
+        <v>27</v>
+      </c>
+      <c r="I37" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="121.5">
       <c r="A38" s="2" t="s">
-        <v>47</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D38" s="4">
         <v>1</v>
       </c>
+      <c r="E38" s="4">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4">
+        <v>1</v>
+      </c>
       <c r="G38" s="2" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="2"/>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="2"/>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="2"/>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="I38" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="94.5">
+      <c r="A39" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" s="4">
+        <v>1</v>
+      </c>
+      <c r="E39" s="4">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I39" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="175.5">
+      <c r="A40" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D40" s="4">
+        <v>1</v>
+      </c>
+      <c r="E40" s="4">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I40" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="135">
+      <c r="A41" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D41" s="4">
+        <v>1</v>
+      </c>
+      <c r="E41" s="4">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I41" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="202.5">
+      <c r="A42" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1</v>
+      </c>
+      <c r="E42" s="4">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I42" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="108">
+      <c r="A43" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" s="4">
+        <v>1</v>
+      </c>
+      <c r="E43" s="4">
+        <v>2</v>
+      </c>
+      <c r="F43" s="4">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I43" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="121.5">
+      <c r="A44" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="4">
+        <v>1</v>
+      </c>
+      <c r="E44" s="4">
+        <v>2</v>
+      </c>
+      <c r="F44" s="4">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I44" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="108">
+      <c r="A45" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1</v>
+      </c>
+      <c r="E45" s="4">
+        <v>2</v>
+      </c>
+      <c r="F45" s="4">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I45" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="108">
+      <c r="A46" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D46" s="4">
+        <v>1</v>
+      </c>
+      <c r="E46" s="4">
+        <v>2</v>
+      </c>
+      <c r="F46" s="4">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I46" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="148.5">
+      <c r="A47" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" s="4">
+        <v>1</v>
+      </c>
+      <c r="E47" s="4">
+        <v>2</v>
+      </c>
+      <c r="F47" s="4">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I47" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="108">
+      <c r="A48" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D48" s="4">
+        <v>1</v>
+      </c>
+      <c r="E48" s="4">
+        <v>2</v>
+      </c>
+      <c r="F48" s="4">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I48" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="94.5">
+      <c r="A49" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" s="4">
+        <v>1</v>
+      </c>
+      <c r="E49" s="4">
+        <v>2</v>
+      </c>
+      <c r="F49" s="4">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I49" s="4">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>